--- a/PNAP-MIS-member-credentials-2026-08-14.xlsx
+++ b/PNAP-MIS-member-credentials-2026-08-14.xlsx
@@ -1,12 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65B050D1-318D-4CDC-9E45-1D419D8477BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Members" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Role Holders" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="How To Log In" state="visible" r:id="rId6"/>
+    <sheet name="Members" sheetId="1" r:id="rId1"/>
+    <sheet name="Role Holders" sheetId="2" r:id="rId2"/>
+    <sheet name="How To Log In" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -7479,33 +7483,53 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9AA5B1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0A3A6E"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFB42318"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF9AA5B1"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF0A3A6E"/>
-    </font>
-    <font>
-      <color rgb="FFB42318"/>
-    </font>
-    <font/>
-    <font>
-      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -7535,10 +7559,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -7558,8 +7583,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -7896,9 +7923,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O385"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -7916,7 +7943,7 @@
     <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7963,7 +7990,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" s="2" customFormat="1">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -8010,7 +8037,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8057,7 +8084,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" s="2" customFormat="1">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -8104,7 +8131,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8151,7 +8178,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15" s="2" customFormat="1">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -8198,7 +8225,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8245,7 +8272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" s="2" customFormat="1">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -8292,7 +8319,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8339,7 +8366,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" s="2" customFormat="1">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -8386,7 +8413,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8433,7 +8460,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15" s="2" customFormat="1">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -8480,7 +8507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8527,7 +8554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15" s="2" customFormat="1">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -8574,7 +8601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8621,7 +8648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15" s="2" customFormat="1">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -8668,7 +8695,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8715,7 +8742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" s="2" customFormat="1">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -8762,7 +8789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8796,7 +8823,7 @@
       <c r="K19" t="s">
         <v>136</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" s="13" t="s">
         <v>137</v>
       </c>
       <c r="M19" t="s">
@@ -8809,7 +8836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" s="2" customFormat="1">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -8856,7 +8883,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8903,7 +8930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" s="2" customFormat="1">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -8950,7 +8977,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8997,7 +9024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" s="2" customFormat="1">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -9044,7 +9071,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -9091,7 +9118,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" s="2" customFormat="1">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -9138,7 +9165,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -9185,7 +9212,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" s="2" customFormat="1">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -9232,7 +9259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -9279,7 +9306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" s="2" customFormat="1">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -9326,7 +9353,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -9373,7 +9400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" s="2" customFormat="1">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -9420,7 +9447,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -9467,7 +9494,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" s="2" customFormat="1">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -9514,7 +9541,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -9561,7 +9588,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" s="2" customFormat="1">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -9608,7 +9635,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -9655,7 +9682,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" s="2" customFormat="1">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -9702,7 +9729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -9749,7 +9776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" s="2" customFormat="1">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -9796,7 +9823,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -9843,7 +9870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" s="2" customFormat="1">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -9890,7 +9917,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -9937,7 +9964,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" s="2" customFormat="1">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -9984,7 +10011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -10031,7 +10058,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" s="2" customFormat="1">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -10078,7 +10105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -10125,7 +10152,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" s="2" customFormat="1">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -10172,7 +10199,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -10219,7 +10246,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" s="2" customFormat="1">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -10266,7 +10293,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -10313,7 +10340,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" s="2" customFormat="1">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -10360,7 +10387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -10407,7 +10434,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" s="2" customFormat="1">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -10454,7 +10481,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -10501,7 +10528,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" s="2" customFormat="1">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -10548,7 +10575,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -10595,7 +10622,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" s="2" customFormat="1">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -10642,7 +10669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -10689,7 +10716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" s="2" customFormat="1">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -10736,7 +10763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -10783,7 +10810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" s="2" customFormat="1">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -10830,7 +10857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -10877,7 +10904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" s="2" customFormat="1">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -10924,7 +10951,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -10971,7 +10998,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" s="2" customFormat="1">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -11018,7 +11045,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15">
       <c r="A67">
         <v>66</v>
       </c>
@@ -11065,7 +11092,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" s="2" customFormat="1">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -11112,7 +11139,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15">
       <c r="A69">
         <v>68</v>
       </c>
@@ -11159,7 +11186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" s="2" customFormat="1">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -11206,7 +11233,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -11253,7 +11280,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" s="2" customFormat="1">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -11300,7 +11327,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -11347,7 +11374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" s="2" customFormat="1">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -11394,7 +11421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -11441,7 +11468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" s="2" customFormat="1">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -11488,7 +11515,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15">
       <c r="A77">
         <v>76</v>
       </c>
@@ -11535,7 +11562,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" s="2" customFormat="1">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -11582,7 +11609,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15">
       <c r="A79">
         <v>78</v>
       </c>
@@ -11629,7 +11656,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" s="2" customFormat="1">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -11676,7 +11703,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15">
       <c r="A81">
         <v>80</v>
       </c>
@@ -11723,7 +11750,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" s="2" customFormat="1">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -11770,7 +11797,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15">
       <c r="A83">
         <v>82</v>
       </c>
@@ -11817,7 +11844,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" s="2" customFormat="1">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -11864,7 +11891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15">
       <c r="A85">
         <v>84</v>
       </c>
@@ -11911,7 +11938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" s="2" customFormat="1">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -11958,7 +11985,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15">
       <c r="A87">
         <v>86</v>
       </c>
@@ -12005,7 +12032,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" s="2" customFormat="1">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -12052,7 +12079,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15">
       <c r="A89">
         <v>88</v>
       </c>
@@ -12099,7 +12126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" s="2" customFormat="1">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -12146,7 +12173,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15">
       <c r="A91">
         <v>90</v>
       </c>
@@ -12193,7 +12220,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" s="2" customFormat="1">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -12240,7 +12267,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15">
       <c r="A93">
         <v>92</v>
       </c>
@@ -12287,7 +12314,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" s="2" customFormat="1">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -12334,7 +12361,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15">
       <c r="A95">
         <v>94</v>
       </c>
@@ -12381,7 +12408,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" s="2" customFormat="1">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -12428,7 +12455,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15">
       <c r="A97">
         <v>96</v>
       </c>
@@ -12475,7 +12502,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" s="2" customFormat="1">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -12522,7 +12549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15">
       <c r="A99">
         <v>98</v>
       </c>
@@ -12569,7 +12596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" s="2" customFormat="1">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -12616,7 +12643,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15">
       <c r="A101">
         <v>100</v>
       </c>
@@ -12663,7 +12690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" s="2" customFormat="1">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -12710,7 +12737,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15">
       <c r="A103">
         <v>102</v>
       </c>
@@ -12757,7 +12784,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" s="2" customFormat="1">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -12804,7 +12831,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15">
       <c r="A105">
         <v>104</v>
       </c>
@@ -12851,7 +12878,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" s="2" customFormat="1">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -12898,7 +12925,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15">
       <c r="A107">
         <v>106</v>
       </c>
@@ -12945,7 +12972,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" s="2" customFormat="1">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -12992,7 +13019,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15">
       <c r="A109">
         <v>108</v>
       </c>
@@ -13039,7 +13066,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" s="2" customFormat="1">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -13086,7 +13113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15">
       <c r="A111">
         <v>110</v>
       </c>
@@ -13133,7 +13160,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" s="2" customFormat="1">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -13180,7 +13207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15">
       <c r="A113">
         <v>112</v>
       </c>
@@ -13227,7 +13254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" s="2" customFormat="1">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -13274,7 +13301,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15">
       <c r="A115">
         <v>114</v>
       </c>
@@ -13321,7 +13348,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" s="2" customFormat="1">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -13368,7 +13395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15">
       <c r="A117">
         <v>116</v>
       </c>
@@ -13415,7 +13442,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" s="2" customFormat="1">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -13462,7 +13489,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15">
       <c r="A119">
         <v>118</v>
       </c>
@@ -13509,7 +13536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" s="2" customFormat="1">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -13556,7 +13583,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15">
       <c r="A121">
         <v>120</v>
       </c>
@@ -13603,7 +13630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" s="2" customFormat="1">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -13650,7 +13677,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15">
       <c r="A123">
         <v>122</v>
       </c>
@@ -13697,7 +13724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" s="2" customFormat="1">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -13744,7 +13771,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15">
       <c r="A125">
         <v>124</v>
       </c>
@@ -13791,7 +13818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" s="2" customFormat="1">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -13838,7 +13865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15">
       <c r="A127">
         <v>126</v>
       </c>
@@ -13885,7 +13912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" s="2" customFormat="1">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -13932,7 +13959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15">
       <c r="A129">
         <v>128</v>
       </c>
@@ -13979,7 +14006,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" s="2" customFormat="1">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -14026,7 +14053,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15">
       <c r="A131">
         <v>130</v>
       </c>
@@ -14073,7 +14100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" s="2" customFormat="1">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -14120,7 +14147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15">
       <c r="A133">
         <v>132</v>
       </c>
@@ -14167,7 +14194,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" s="2" customFormat="1">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -14214,7 +14241,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15">
       <c r="A135">
         <v>134</v>
       </c>
@@ -14261,7 +14288,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" s="2" customFormat="1">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -14308,7 +14335,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15">
       <c r="A137">
         <v>136</v>
       </c>
@@ -14355,7 +14382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" s="2" customFormat="1">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -14402,7 +14429,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15">
       <c r="A139">
         <v>138</v>
       </c>
@@ -14449,7 +14476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" s="2" customFormat="1">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -14496,7 +14523,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15">
       <c r="A141">
         <v>140</v>
       </c>
@@ -14543,7 +14570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" s="2" customFormat="1">
       <c r="A142" s="2">
         <v>141</v>
       </c>
@@ -14590,7 +14617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15">
       <c r="A143">
         <v>142</v>
       </c>
@@ -14637,7 +14664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" s="2" customFormat="1">
       <c r="A144" s="2">
         <v>143</v>
       </c>
@@ -14684,7 +14711,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15">
       <c r="A145">
         <v>144</v>
       </c>
@@ -14731,7 +14758,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" s="2" customFormat="1">
       <c r="A146" s="2">
         <v>145</v>
       </c>
@@ -14778,7 +14805,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15">
       <c r="A147">
         <v>146</v>
       </c>
@@ -14825,7 +14852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" s="2" customFormat="1">
       <c r="A148" s="2">
         <v>147</v>
       </c>
@@ -14872,7 +14899,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15">
       <c r="A149">
         <v>148</v>
       </c>
@@ -14919,7 +14946,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" s="2" customFormat="1">
       <c r="A150" s="2">
         <v>149</v>
       </c>
@@ -14966,7 +14993,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15">
       <c r="A151">
         <v>150</v>
       </c>
@@ -15013,7 +15040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" s="2" customFormat="1">
       <c r="A152" s="2">
         <v>151</v>
       </c>
@@ -15060,7 +15087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15">
       <c r="A153">
         <v>152</v>
       </c>
@@ -15107,7 +15134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" s="2" customFormat="1">
       <c r="A154" s="2">
         <v>153</v>
       </c>
@@ -15154,7 +15181,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15">
       <c r="A155">
         <v>154</v>
       </c>
@@ -15201,7 +15228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" s="2" customFormat="1">
       <c r="A156" s="2">
         <v>155</v>
       </c>
@@ -15248,7 +15275,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15">
       <c r="A157">
         <v>156</v>
       </c>
@@ -15295,7 +15322,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" s="2" customFormat="1">
       <c r="A158" s="2">
         <v>157</v>
       </c>
@@ -15342,7 +15369,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15">
       <c r="A159">
         <v>158</v>
       </c>
@@ -15389,7 +15416,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" s="2" customFormat="1">
       <c r="A160" s="2">
         <v>159</v>
       </c>
@@ -15436,7 +15463,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15">
       <c r="A161">
         <v>160</v>
       </c>
@@ -15483,7 +15510,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15" s="2" customFormat="1">
       <c r="A162" s="2">
         <v>161</v>
       </c>
@@ -15530,7 +15557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15">
       <c r="A163">
         <v>162</v>
       </c>
@@ -15577,7 +15604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15" s="2" customFormat="1">
       <c r="A164" s="2">
         <v>163</v>
       </c>
@@ -15624,7 +15651,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15">
       <c r="A165">
         <v>164</v>
       </c>
@@ -15671,7 +15698,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15" s="2" customFormat="1">
       <c r="A166" s="2">
         <v>165</v>
       </c>
@@ -15718,7 +15745,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15">
       <c r="A167">
         <v>166</v>
       </c>
@@ -15765,7 +15792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15" s="2" customFormat="1">
       <c r="A168" s="2">
         <v>167</v>
       </c>
@@ -15812,7 +15839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15">
       <c r="A169">
         <v>168</v>
       </c>
@@ -15859,7 +15886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15" s="2" customFormat="1">
       <c r="A170" s="2">
         <v>169</v>
       </c>
@@ -15906,7 +15933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15">
       <c r="A171">
         <v>170</v>
       </c>
@@ -15953,7 +15980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15" s="2" customFormat="1">
       <c r="A172" s="2">
         <v>171</v>
       </c>
@@ -16000,7 +16027,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15">
       <c r="A173">
         <v>172</v>
       </c>
@@ -16047,7 +16074,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" s="2" customFormat="1">
       <c r="A174" s="2">
         <v>173</v>
       </c>
@@ -16094,7 +16121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15">
       <c r="A175">
         <v>174</v>
       </c>
@@ -16141,7 +16168,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15" s="2" customFormat="1">
       <c r="A176" s="2">
         <v>175</v>
       </c>
@@ -16188,7 +16215,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15">
       <c r="A177">
         <v>176</v>
       </c>
@@ -16235,7 +16262,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15" s="2" customFormat="1">
       <c r="A178" s="2">
         <v>177</v>
       </c>
@@ -16282,7 +16309,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15">
       <c r="A179">
         <v>178</v>
       </c>
@@ -16329,7 +16356,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15" s="2" customFormat="1">
       <c r="A180" s="2">
         <v>179</v>
       </c>
@@ -16376,7 +16403,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15">
       <c r="A181">
         <v>180</v>
       </c>
@@ -16423,7 +16450,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15" s="2" customFormat="1">
       <c r="A182" s="2">
         <v>181</v>
       </c>
@@ -16470,7 +16497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15">
       <c r="A183">
         <v>182</v>
       </c>
@@ -16517,7 +16544,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15" s="2" customFormat="1">
       <c r="A184" s="2">
         <v>183</v>
       </c>
@@ -16564,7 +16591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15">
       <c r="A185">
         <v>184</v>
       </c>
@@ -16611,7 +16638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15" s="2" customFormat="1">
       <c r="A186" s="2">
         <v>185</v>
       </c>
@@ -16658,7 +16685,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15">
       <c r="A187">
         <v>186</v>
       </c>
@@ -16705,7 +16732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15" s="2" customFormat="1">
       <c r="A188" s="2">
         <v>187</v>
       </c>
@@ -16752,7 +16779,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15">
       <c r="A189">
         <v>188</v>
       </c>
@@ -16799,7 +16826,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15" s="2" customFormat="1">
       <c r="A190" s="2">
         <v>189</v>
       </c>
@@ -16846,7 +16873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15">
       <c r="A191">
         <v>190</v>
       </c>
@@ -16893,7 +16920,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15" s="2" customFormat="1">
       <c r="A192" s="2">
         <v>191</v>
       </c>
@@ -16940,7 +16967,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15">
       <c r="A193">
         <v>192</v>
       </c>
@@ -16987,7 +17014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15" s="2" customFormat="1">
       <c r="A194" s="2">
         <v>193</v>
       </c>
@@ -17034,7 +17061,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15">
       <c r="A195">
         <v>194</v>
       </c>
@@ -17081,7 +17108,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15" s="2" customFormat="1">
       <c r="A196" s="2">
         <v>195</v>
       </c>
@@ -17128,7 +17155,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15">
       <c r="A197">
         <v>196</v>
       </c>
@@ -17175,7 +17202,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15" s="2" customFormat="1">
       <c r="A198" s="2">
         <v>197</v>
       </c>
@@ -17222,7 +17249,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15">
       <c r="A199">
         <v>198</v>
       </c>
@@ -17269,7 +17296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15" s="2" customFormat="1">
       <c r="A200" s="2">
         <v>199</v>
       </c>
@@ -17316,7 +17343,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15">
       <c r="A201">
         <v>200</v>
       </c>
@@ -17363,7 +17390,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" s="2" customFormat="1">
       <c r="A202" s="2">
         <v>201</v>
       </c>
@@ -17410,7 +17437,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15">
       <c r="A203">
         <v>202</v>
       </c>
@@ -17457,7 +17484,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15" s="2" customFormat="1">
       <c r="A204" s="2">
         <v>203</v>
       </c>
@@ -17504,7 +17531,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15">
       <c r="A205">
         <v>204</v>
       </c>
@@ -17551,7 +17578,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15" s="2" customFormat="1">
       <c r="A206" s="2">
         <v>205</v>
       </c>
@@ -17598,7 +17625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15">
       <c r="A207">
         <v>206</v>
       </c>
@@ -17645,7 +17672,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15" s="2" customFormat="1">
       <c r="A208" s="2">
         <v>207</v>
       </c>
@@ -17692,7 +17719,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15">
       <c r="A209">
         <v>208</v>
       </c>
@@ -17739,7 +17766,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15" s="2" customFormat="1">
       <c r="A210" s="2">
         <v>209</v>
       </c>
@@ -17786,7 +17813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15">
       <c r="A211">
         <v>210</v>
       </c>
@@ -17833,7 +17860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15" s="2" customFormat="1">
       <c r="A212" s="2">
         <v>211</v>
       </c>
@@ -17880,7 +17907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15">
       <c r="A213">
         <v>212</v>
       </c>
@@ -17927,7 +17954,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15" s="2" customFormat="1">
       <c r="A214" s="2">
         <v>213</v>
       </c>
@@ -17974,7 +18001,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15">
       <c r="A215">
         <v>214</v>
       </c>
@@ -18021,7 +18048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15" s="2" customFormat="1">
       <c r="A216" s="2">
         <v>215</v>
       </c>
@@ -18068,7 +18095,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15">
       <c r="A217">
         <v>216</v>
       </c>
@@ -18115,7 +18142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15" s="2" customFormat="1">
       <c r="A218" s="2">
         <v>217</v>
       </c>
@@ -18162,7 +18189,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15">
       <c r="A219">
         <v>218</v>
       </c>
@@ -18209,7 +18236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15" s="2" customFormat="1">
       <c r="A220" s="2">
         <v>219</v>
       </c>
@@ -18256,7 +18283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15">
       <c r="A221">
         <v>220</v>
       </c>
@@ -18303,7 +18330,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15" s="2" customFormat="1">
       <c r="A222" s="2">
         <v>221</v>
       </c>
@@ -18350,7 +18377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15">
       <c r="A223">
         <v>222</v>
       </c>
@@ -18397,7 +18424,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15" s="2" customFormat="1">
       <c r="A224" s="2">
         <v>223</v>
       </c>
@@ -18444,7 +18471,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15">
       <c r="A225">
         <v>224</v>
       </c>
@@ -18491,7 +18518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15" s="2" customFormat="1">
       <c r="A226" s="2">
         <v>225</v>
       </c>
@@ -18538,7 +18565,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15">
       <c r="A227">
         <v>226</v>
       </c>
@@ -18585,7 +18612,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15" s="2" customFormat="1">
       <c r="A228" s="2">
         <v>227</v>
       </c>
@@ -18632,7 +18659,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15">
       <c r="A229">
         <v>228</v>
       </c>
@@ -18679,7 +18706,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15" s="2" customFormat="1">
       <c r="A230" s="2">
         <v>229</v>
       </c>
@@ -18726,7 +18753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15">
       <c r="A231">
         <v>230</v>
       </c>
@@ -18773,7 +18800,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" s="2" customFormat="1">
       <c r="A232" s="2">
         <v>231</v>
       </c>
@@ -18820,7 +18847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15">
       <c r="A233">
         <v>232</v>
       </c>
@@ -18867,7 +18894,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15" s="2" customFormat="1">
       <c r="A234" s="2">
         <v>233</v>
       </c>
@@ -18914,7 +18941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15">
       <c r="A235">
         <v>234</v>
       </c>
@@ -18961,7 +18988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15" s="2" customFormat="1">
       <c r="A236" s="2">
         <v>235</v>
       </c>
@@ -19008,7 +19035,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15">
       <c r="A237">
         <v>236</v>
       </c>
@@ -19055,7 +19082,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15" s="2" customFormat="1">
       <c r="A238" s="2">
         <v>237</v>
       </c>
@@ -19102,7 +19129,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15">
       <c r="A239">
         <v>238</v>
       </c>
@@ -19149,7 +19176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15" s="2" customFormat="1">
       <c r="A240" s="2">
         <v>239</v>
       </c>
@@ -19196,7 +19223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15">
       <c r="A241">
         <v>240</v>
       </c>
@@ -19243,7 +19270,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15" s="2" customFormat="1">
       <c r="A242" s="2">
         <v>241</v>
       </c>
@@ -19290,7 +19317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15">
       <c r="A243">
         <v>242</v>
       </c>
@@ -19337,7 +19364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15" s="2" customFormat="1">
       <c r="A244" s="2">
         <v>243</v>
       </c>
@@ -19384,7 +19411,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15">
       <c r="A245">
         <v>244</v>
       </c>
@@ -19431,7 +19458,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="246" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15" s="2" customFormat="1">
       <c r="A246" s="2">
         <v>245</v>
       </c>
@@ -19478,7 +19505,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15">
       <c r="A247">
         <v>246</v>
       </c>
@@ -19525,7 +19552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="248" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15" s="2" customFormat="1">
       <c r="A248" s="2">
         <v>247</v>
       </c>
@@ -19572,7 +19599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15">
       <c r="A249">
         <v>248</v>
       </c>
@@ -19619,7 +19646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="250" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15" s="2" customFormat="1">
       <c r="A250" s="2">
         <v>249</v>
       </c>
@@ -19666,7 +19693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15">
       <c r="A251">
         <v>250</v>
       </c>
@@ -19713,7 +19740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15" s="2" customFormat="1">
       <c r="A252" s="2">
         <v>251</v>
       </c>
@@ -19760,7 +19787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15">
       <c r="A253">
         <v>252</v>
       </c>
@@ -19807,7 +19834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="254" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15" s="2" customFormat="1">
       <c r="A254" s="2">
         <v>253</v>
       </c>
@@ -19854,7 +19881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15">
       <c r="A255">
         <v>254</v>
       </c>
@@ -19901,7 +19928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15" s="2" customFormat="1">
       <c r="A256" s="2">
         <v>255</v>
       </c>
@@ -19948,7 +19975,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15">
       <c r="A257">
         <v>256</v>
       </c>
@@ -19995,7 +20022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15" s="2" customFormat="1">
       <c r="A258" s="2">
         <v>257</v>
       </c>
@@ -20042,7 +20069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15">
       <c r="A259">
         <v>258</v>
       </c>
@@ -20089,7 +20116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="260" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" s="2" customFormat="1">
       <c r="A260" s="2">
         <v>259</v>
       </c>
@@ -20136,7 +20163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15">
       <c r="A261">
         <v>260</v>
       </c>
@@ -20183,7 +20210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="262" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15" s="2" customFormat="1">
       <c r="A262" s="2">
         <v>261</v>
       </c>
@@ -20230,7 +20257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15">
       <c r="A263">
         <v>262</v>
       </c>
@@ -20277,7 +20304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="264" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15" s="2" customFormat="1">
       <c r="A264" s="2">
         <v>263</v>
       </c>
@@ -20324,7 +20351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15">
       <c r="A265">
         <v>264</v>
       </c>
@@ -20371,7 +20398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="266" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15" s="2" customFormat="1">
       <c r="A266" s="2">
         <v>265</v>
       </c>
@@ -20418,7 +20445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15">
       <c r="A267">
         <v>266</v>
       </c>
@@ -20465,7 +20492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="268" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15" s="2" customFormat="1">
       <c r="A268" s="2">
         <v>267</v>
       </c>
@@ -20512,7 +20539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15">
       <c r="A269">
         <v>268</v>
       </c>
@@ -20559,7 +20586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="270" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15" s="2" customFormat="1">
       <c r="A270" s="2">
         <v>269</v>
       </c>
@@ -20606,7 +20633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15">
       <c r="A271">
         <v>270</v>
       </c>
@@ -20653,7 +20680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="272" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15" s="2" customFormat="1">
       <c r="A272" s="2">
         <v>271</v>
       </c>
@@ -20700,7 +20727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15">
       <c r="A273">
         <v>272</v>
       </c>
@@ -20747,7 +20774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15" s="2" customFormat="1">
       <c r="A274" s="2">
         <v>273</v>
       </c>
@@ -20794,7 +20821,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15">
       <c r="A275">
         <v>274</v>
       </c>
@@ -20841,7 +20868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="276" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15" s="2" customFormat="1">
       <c r="A276" s="2">
         <v>275</v>
       </c>
@@ -20888,7 +20915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15">
       <c r="A277">
         <v>276</v>
       </c>
@@ -20935,7 +20962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="278" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15" s="2" customFormat="1">
       <c r="A278" s="2">
         <v>277</v>
       </c>
@@ -20982,7 +21009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15">
       <c r="A279">
         <v>278</v>
       </c>
@@ -21029,7 +21056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15" s="2" customFormat="1">
       <c r="A280" s="2">
         <v>279</v>
       </c>
@@ -21076,7 +21103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15">
       <c r="A281">
         <v>280</v>
       </c>
@@ -21123,7 +21150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="282" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15" s="2" customFormat="1">
       <c r="A282" s="2">
         <v>281</v>
       </c>
@@ -21170,7 +21197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15">
       <c r="A283">
         <v>282</v>
       </c>
@@ -21217,7 +21244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="284" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" s="2" customFormat="1">
       <c r="A284" s="2">
         <v>283</v>
       </c>
@@ -21264,7 +21291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:15">
       <c r="A285">
         <v>284</v>
       </c>
@@ -21311,7 +21338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="286" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:15" s="2" customFormat="1">
       <c r="A286" s="2">
         <v>285</v>
       </c>
@@ -21358,7 +21385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:15">
       <c r="A287">
         <v>286</v>
       </c>
@@ -21405,7 +21432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="288" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:15" s="2" customFormat="1">
       <c r="A288" s="2">
         <v>287</v>
       </c>
@@ -21452,7 +21479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15">
       <c r="A289">
         <v>288</v>
       </c>
@@ -21499,7 +21526,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" s="2" customFormat="1">
       <c r="A290" s="2">
         <v>289</v>
       </c>
@@ -21546,7 +21573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:15">
       <c r="A291">
         <v>290</v>
       </c>
@@ -21593,7 +21620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="292" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:15" s="2" customFormat="1">
       <c r="A292" s="2">
         <v>291</v>
       </c>
@@ -21640,7 +21667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:15">
       <c r="A293">
         <v>292</v>
       </c>
@@ -21687,7 +21714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="294" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:15" s="2" customFormat="1">
       <c r="A294" s="2">
         <v>293</v>
       </c>
@@ -21734,7 +21761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:15">
       <c r="A295">
         <v>294</v>
       </c>
@@ -21781,7 +21808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="296" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:15" s="2" customFormat="1">
       <c r="A296" s="2">
         <v>295</v>
       </c>
@@ -21828,7 +21855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:15">
       <c r="A297">
         <v>296</v>
       </c>
@@ -21875,7 +21902,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="298" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:15" s="2" customFormat="1">
       <c r="A298" s="2">
         <v>297</v>
       </c>
@@ -21922,7 +21949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:15">
       <c r="A299">
         <v>298</v>
       </c>
@@ -21969,7 +21996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="300" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:15" s="2" customFormat="1">
       <c r="A300" s="2">
         <v>299</v>
       </c>
@@ -22016,7 +22043,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:15">
       <c r="A301">
         <v>300</v>
       </c>
@@ -22063,7 +22090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="302" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:15" s="2" customFormat="1">
       <c r="A302" s="2">
         <v>301</v>
       </c>
@@ -22110,7 +22137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:15">
       <c r="A303">
         <v>302</v>
       </c>
@@ -22157,7 +22184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="304" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:15" s="2" customFormat="1">
       <c r="A304" s="2">
         <v>303</v>
       </c>
@@ -22204,7 +22231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:15">
       <c r="A305">
         <v>304</v>
       </c>
@@ -22251,7 +22278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:15" s="2" customFormat="1">
       <c r="A306" s="2">
         <v>305</v>
       </c>
@@ -22298,7 +22325,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:15">
       <c r="A307">
         <v>306</v>
       </c>
@@ -22345,7 +22372,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="308" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:15" s="2" customFormat="1">
       <c r="A308" s="2">
         <v>307</v>
       </c>
@@ -22392,7 +22419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:15">
       <c r="A309">
         <v>308</v>
       </c>
@@ -22439,7 +22466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="310" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:15" s="2" customFormat="1">
       <c r="A310" s="2">
         <v>309</v>
       </c>
@@ -22486,7 +22513,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:15">
       <c r="A311">
         <v>310</v>
       </c>
@@ -22533,7 +22560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="312" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:15" s="2" customFormat="1">
       <c r="A312" s="2">
         <v>311</v>
       </c>
@@ -22580,7 +22607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:15">
       <c r="A313">
         <v>312</v>
       </c>
@@ -22627,7 +22654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="314" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:15" s="2" customFormat="1">
       <c r="A314" s="2">
         <v>313</v>
       </c>
@@ -22674,7 +22701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:15">
       <c r="A315">
         <v>314</v>
       </c>
@@ -22721,7 +22748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="316" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:15" s="2" customFormat="1">
       <c r="A316" s="2">
         <v>315</v>
       </c>
@@ -22768,7 +22795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:15">
       <c r="A317">
         <v>316</v>
       </c>
@@ -22815,7 +22842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="318" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" s="2" customFormat="1">
       <c r="A318" s="2">
         <v>317</v>
       </c>
@@ -22862,7 +22889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15">
       <c r="A319">
         <v>318</v>
       </c>
@@ -22909,7 +22936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="320" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:15" s="2" customFormat="1">
       <c r="A320" s="2">
         <v>319</v>
       </c>
@@ -22956,7 +22983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:15">
       <c r="A321">
         <v>320</v>
       </c>
@@ -23003,7 +23030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="322" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:15" s="2" customFormat="1">
       <c r="A322" s="2">
         <v>321</v>
       </c>
@@ -23050,7 +23077,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:15">
       <c r="A323">
         <v>322</v>
       </c>
@@ -23097,7 +23124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="324" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:15" s="2" customFormat="1">
       <c r="A324" s="2">
         <v>323</v>
       </c>
@@ -23144,7 +23171,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:15">
       <c r="A325">
         <v>324</v>
       </c>
@@ -23191,7 +23218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="326" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:15" s="2" customFormat="1">
       <c r="A326" s="2">
         <v>325</v>
       </c>
@@ -23238,7 +23265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:15">
       <c r="A327">
         <v>326</v>
       </c>
@@ -23285,7 +23312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="328" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:15" s="2" customFormat="1">
       <c r="A328" s="2">
         <v>327</v>
       </c>
@@ -23332,7 +23359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:15">
       <c r="A329">
         <v>328</v>
       </c>
@@ -23379,7 +23406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="330" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:15" s="2" customFormat="1">
       <c r="A330" s="2">
         <v>329</v>
       </c>
@@ -23426,7 +23453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="331" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:15">
       <c r="A331">
         <v>330</v>
       </c>
@@ -23473,7 +23500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="332" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:15" s="2" customFormat="1">
       <c r="A332" s="2">
         <v>331</v>
       </c>
@@ -23520,7 +23547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="333" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:15">
       <c r="A333">
         <v>332</v>
       </c>
@@ -23567,7 +23594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="334" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:15" s="2" customFormat="1">
       <c r="A334" s="2">
         <v>333</v>
       </c>
@@ -23614,7 +23641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="335" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:15">
       <c r="A335">
         <v>334</v>
       </c>
@@ -23661,7 +23688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="336" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:15" s="2" customFormat="1">
       <c r="A336" s="2">
         <v>335</v>
       </c>
@@ -23708,7 +23735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:15">
       <c r="A337">
         <v>336</v>
       </c>
@@ -23755,7 +23782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="338" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:15" s="2" customFormat="1">
       <c r="A338" s="2">
         <v>337</v>
       </c>
@@ -23802,7 +23829,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:15">
       <c r="A339">
         <v>338</v>
       </c>
@@ -23849,7 +23876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="340" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:15" s="2" customFormat="1">
       <c r="A340" s="2">
         <v>339</v>
       </c>
@@ -23896,7 +23923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:15">
       <c r="A341">
         <v>340</v>
       </c>
@@ -23943,7 +23970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:15" s="2" customFormat="1">
       <c r="A342" s="2">
         <v>341</v>
       </c>
@@ -23990,7 +24017,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:15">
       <c r="A343">
         <v>342</v>
       </c>
@@ -24037,7 +24064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="344" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:15" s="2" customFormat="1">
       <c r="A344" s="2">
         <v>343</v>
       </c>
@@ -24084,7 +24111,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:15">
       <c r="A345">
         <v>344</v>
       </c>
@@ -24131,7 +24158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="346" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:15" s="2" customFormat="1">
       <c r="A346" s="2">
         <v>345</v>
       </c>
@@ -24178,7 +24205,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15">
       <c r="A347">
         <v>346</v>
       </c>
@@ -24225,7 +24252,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="348" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" s="2" customFormat="1">
       <c r="A348" s="2">
         <v>347</v>
       </c>
@@ -24272,7 +24299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:15">
       <c r="A349">
         <v>348</v>
       </c>
@@ -24319,7 +24346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:15" s="2" customFormat="1">
       <c r="A350" s="2">
         <v>349</v>
       </c>
@@ -24366,7 +24393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:15">
       <c r="A351">
         <v>350</v>
       </c>
@@ -24413,7 +24440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="352" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:15" s="2" customFormat="1">
       <c r="A352" s="2">
         <v>351</v>
       </c>
@@ -24460,7 +24487,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:15">
       <c r="A353">
         <v>352</v>
       </c>
@@ -24507,7 +24534,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:15" s="2" customFormat="1">
       <c r="A354" s="2">
         <v>353</v>
       </c>
@@ -24554,7 +24581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:15">
       <c r="A355">
         <v>354</v>
       </c>
@@ -24601,7 +24628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:15" s="2" customFormat="1">
       <c r="A356" s="2">
         <v>355</v>
       </c>
@@ -24648,7 +24675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:15">
       <c r="A357">
         <v>356</v>
       </c>
@@ -24695,7 +24722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="358" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:15" s="2" customFormat="1">
       <c r="A358" s="2">
         <v>357</v>
       </c>
@@ -24742,7 +24769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:15">
       <c r="A359">
         <v>358</v>
       </c>
@@ -24789,7 +24816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:15" s="2" customFormat="1">
       <c r="A360" s="2">
         <v>359</v>
       </c>
@@ -24836,7 +24863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:15">
       <c r="A361">
         <v>360</v>
       </c>
@@ -24883,7 +24910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="362" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:15" s="2" customFormat="1">
       <c r="A362" s="2">
         <v>361</v>
       </c>
@@ -24930,7 +24957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:15">
       <c r="A363">
         <v>362</v>
       </c>
@@ -24977,7 +25004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="364" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:15" s="2" customFormat="1">
       <c r="A364" s="2">
         <v>363</v>
       </c>
@@ -25024,7 +25051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:15">
       <c r="A365">
         <v>364</v>
       </c>
@@ -25071,7 +25098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="366" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:15" s="2" customFormat="1">
       <c r="A366" s="2">
         <v>365</v>
       </c>
@@ -25118,7 +25145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:15">
       <c r="A367">
         <v>366</v>
       </c>
@@ -25165,7 +25192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="368" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:15" s="2" customFormat="1">
       <c r="A368" s="2">
         <v>367</v>
       </c>
@@ -25212,7 +25239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="369" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:15">
       <c r="A369">
         <v>368</v>
       </c>
@@ -25259,7 +25286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="370" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:15" s="2" customFormat="1">
       <c r="A370" s="2">
         <v>369</v>
       </c>
@@ -25306,7 +25333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="371" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:15">
       <c r="A371">
         <v>370</v>
       </c>
@@ -25353,7 +25380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="372" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:15" s="2" customFormat="1">
       <c r="A372" s="2">
         <v>371</v>
       </c>
@@ -25400,7 +25427,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="373" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:15">
       <c r="A373">
         <v>372</v>
       </c>
@@ -25447,7 +25474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="374" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:15" s="2" customFormat="1">
       <c r="A374" s="2">
         <v>373</v>
       </c>
@@ -25494,7 +25521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="375" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:15">
       <c r="A375">
         <v>374</v>
       </c>
@@ -25541,7 +25568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" s="2" customFormat="1">
       <c r="A376" s="2">
         <v>375</v>
       </c>
@@ -25588,7 +25615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="377" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15">
       <c r="A377">
         <v>376</v>
       </c>
@@ -25635,7 +25662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="378" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:15" s="2" customFormat="1">
       <c r="A378" s="2">
         <v>377</v>
       </c>
@@ -25682,7 +25709,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="379" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:15">
       <c r="A379">
         <v>378</v>
       </c>
@@ -25729,7 +25756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="380" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:15" s="2" customFormat="1">
       <c r="A380" s="2">
         <v>379</v>
       </c>
@@ -25776,7 +25803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="381" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:15">
       <c r="A381">
         <v>380</v>
       </c>
@@ -25823,7 +25850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="382" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:15" s="2" customFormat="1">
       <c r="A382" s="2">
         <v>381</v>
       </c>
@@ -25870,7 +25897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="383" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:15">
       <c r="A383">
         <v>382</v>
       </c>
@@ -25917,7 +25944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="384" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:15" s="2" customFormat="1">
       <c r="A384" s="2">
         <v>383</v>
       </c>
@@ -25964,7 +25991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:15">
       <c r="A385">
         <v>384</v>
       </c>
@@ -26012,16 +26039,19 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <hyperlinks>
+    <hyperlink ref="L19" r:id="rId1" xr:uid="{C85C33CC-AE32-4A72-9B3A-B76AF1EC0ABF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O284"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -26039,7 +26069,7 @@
     <col min="15" max="15" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="7" customFormat="1" ht="22" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -26086,7 +26116,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -26133,7 +26163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -26180,7 +26210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -26227,7 +26257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -26274,7 +26304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -26321,7 +26351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -26368,7 +26398,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -26415,7 +26445,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -26462,7 +26492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -26509,7 +26539,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -26556,7 +26586,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -26603,7 +26633,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -26650,7 +26680,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -26697,7 +26727,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -26744,7 +26774,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -26791,7 +26821,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -26838,7 +26868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -26885,7 +26915,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -26932,7 +26962,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -26979,7 +27009,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -27026,7 +27056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -27073,7 +27103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -27120,7 +27150,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -27167,7 +27197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -27214,7 +27244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -27261,7 +27291,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -27308,7 +27338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -27355,7 +27385,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -27402,7 +27432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -27449,7 +27479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -27496,7 +27526,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -27543,7 +27573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -27590,7 +27620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -27637,7 +27667,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -27684,7 +27714,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -27731,7 +27761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -27778,7 +27808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -27825,7 +27855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -27872,7 +27902,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -27919,7 +27949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -27966,7 +27996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -28013,7 +28043,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -28060,7 +28090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -28107,7 +28137,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -28154,7 +28184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -28201,7 +28231,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -28248,7 +28278,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -28295,7 +28325,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -28342,7 +28372,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -28389,7 +28419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -28436,7 +28466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -28483,7 +28513,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -28530,7 +28560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -28577,7 +28607,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -28624,7 +28654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -28671,7 +28701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -28718,7 +28748,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -28765,7 +28795,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -28812,7 +28842,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -28859,7 +28889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -28906,7 +28936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15">
       <c r="A62">
         <v>61</v>
       </c>
@@ -28953,7 +28983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15">
       <c r="A63">
         <v>62</v>
       </c>
@@ -29000,7 +29030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15">
       <c r="A64">
         <v>63</v>
       </c>
@@ -29047,7 +29077,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15">
       <c r="A65">
         <v>64</v>
       </c>
@@ -29094,7 +29124,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15">
       <c r="A66">
         <v>65</v>
       </c>
@@ -29141,7 +29171,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15">
       <c r="A67">
         <v>66</v>
       </c>
@@ -29188,7 +29218,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15">
       <c r="A68">
         <v>67</v>
       </c>
@@ -29235,7 +29265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15">
       <c r="A69">
         <v>68</v>
       </c>
@@ -29282,7 +29312,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15">
       <c r="A70">
         <v>69</v>
       </c>
@@ -29329,7 +29359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15">
       <c r="A71">
         <v>70</v>
       </c>
@@ -29376,7 +29406,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15">
       <c r="A72">
         <v>71</v>
       </c>
@@ -29423,7 +29453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15">
       <c r="A73">
         <v>72</v>
       </c>
@@ -29470,7 +29500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15">
       <c r="A74">
         <v>73</v>
       </c>
@@ -29517,7 +29547,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15">
       <c r="A75">
         <v>74</v>
       </c>
@@ -29564,7 +29594,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15">
       <c r="A76">
         <v>75</v>
       </c>
@@ -29611,7 +29641,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15">
       <c r="A77">
         <v>76</v>
       </c>
@@ -29658,7 +29688,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15">
       <c r="A78">
         <v>77</v>
       </c>
@@ -29705,7 +29735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15">
       <c r="A79">
         <v>78</v>
       </c>
@@ -29752,7 +29782,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15">
       <c r="A80">
         <v>79</v>
       </c>
@@ -29799,7 +29829,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15">
       <c r="A81">
         <v>80</v>
       </c>
@@ -29846,7 +29876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15">
       <c r="A82">
         <v>81</v>
       </c>
@@ -29893,7 +29923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15">
       <c r="A83">
         <v>82</v>
       </c>
@@ -29940,7 +29970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15">
       <c r="A84">
         <v>83</v>
       </c>
@@ -29987,7 +30017,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15">
       <c r="A85">
         <v>84</v>
       </c>
@@ -30034,7 +30064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15">
       <c r="A86">
         <v>85</v>
       </c>
@@ -30081,7 +30111,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15">
       <c r="A87">
         <v>86</v>
       </c>
@@ -30128,7 +30158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15">
       <c r="A88">
         <v>87</v>
       </c>
@@ -30175,7 +30205,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15">
       <c r="A89">
         <v>88</v>
       </c>
@@ -30222,7 +30252,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15">
       <c r="A90">
         <v>89</v>
       </c>
@@ -30269,7 +30299,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15">
       <c r="A91">
         <v>90</v>
       </c>
@@ -30316,7 +30346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15">
       <c r="A92">
         <v>91</v>
       </c>
@@ -30363,7 +30393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15">
       <c r="A93">
         <v>92</v>
       </c>
@@ -30410,7 +30440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15">
       <c r="A94">
         <v>93</v>
       </c>
@@ -30457,7 +30487,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15">
       <c r="A95">
         <v>94</v>
       </c>
@@ -30504,7 +30534,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15">
       <c r="A96">
         <v>95</v>
       </c>
@@ -30551,7 +30581,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15">
       <c r="A97">
         <v>96</v>
       </c>
@@ -30598,7 +30628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15">
       <c r="A98">
         <v>97</v>
       </c>
@@ -30645,7 +30675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15">
       <c r="A99">
         <v>98</v>
       </c>
@@ -30692,7 +30722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15">
       <c r="A100">
         <v>99</v>
       </c>
@@ -30739,7 +30769,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15">
       <c r="A101">
         <v>100</v>
       </c>
@@ -30786,7 +30816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15">
       <c r="A102">
         <v>101</v>
       </c>
@@ -30833,7 +30863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15">
       <c r="A103">
         <v>102</v>
       </c>
@@ -30880,7 +30910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15">
       <c r="A104">
         <v>103</v>
       </c>
@@ -30927,7 +30957,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15">
       <c r="A105">
         <v>104</v>
       </c>
@@ -30974,7 +31004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15">
       <c r="A106">
         <v>105</v>
       </c>
@@ -31021,7 +31051,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15">
       <c r="A107">
         <v>106</v>
       </c>
@@ -31068,7 +31098,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15">
       <c r="A108">
         <v>107</v>
       </c>
@@ -31115,7 +31145,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15">
       <c r="A109">
         <v>108</v>
       </c>
@@ -31162,7 +31192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15">
       <c r="A110">
         <v>109</v>
       </c>
@@ -31209,7 +31239,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15">
       <c r="A111">
         <v>110</v>
       </c>
@@ -31256,7 +31286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15">
       <c r="A112">
         <v>111</v>
       </c>
@@ -31303,7 +31333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15">
       <c r="A113">
         <v>112</v>
       </c>
@@ -31350,7 +31380,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15">
       <c r="A114">
         <v>113</v>
       </c>
@@ -31397,7 +31427,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15">
       <c r="A115">
         <v>114</v>
       </c>
@@ -31444,7 +31474,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15">
       <c r="A116">
         <v>115</v>
       </c>
@@ -31491,7 +31521,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15">
       <c r="A117">
         <v>116</v>
       </c>
@@ -31538,7 +31568,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15">
       <c r="A118">
         <v>117</v>
       </c>
@@ -31585,7 +31615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15">
       <c r="A119">
         <v>118</v>
       </c>
@@ -31632,7 +31662,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15">
       <c r="A120">
         <v>119</v>
       </c>
@@ -31679,7 +31709,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15">
       <c r="A121">
         <v>120</v>
       </c>
@@ -31726,7 +31756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15">
       <c r="A122">
         <v>121</v>
       </c>
@@ -31773,7 +31803,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15">
       <c r="A123">
         <v>122</v>
       </c>
@@ -31820,7 +31850,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15">
       <c r="A124">
         <v>123</v>
       </c>
@@ -31867,7 +31897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15">
       <c r="A125">
         <v>124</v>
       </c>
@@ -31914,7 +31944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15">
       <c r="A126">
         <v>125</v>
       </c>
@@ -31961,7 +31991,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15">
       <c r="A127">
         <v>126</v>
       </c>
@@ -32008,7 +32038,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15">
       <c r="A128">
         <v>127</v>
       </c>
@@ -32055,7 +32085,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15">
       <c r="A129">
         <v>128</v>
       </c>
@@ -32102,7 +32132,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15">
       <c r="A130">
         <v>129</v>
       </c>
@@ -32149,7 +32179,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15">
       <c r="A131">
         <v>130</v>
       </c>
@@ -32196,7 +32226,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15">
       <c r="A132">
         <v>131</v>
       </c>
@@ -32243,7 +32273,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15">
       <c r="A133">
         <v>132</v>
       </c>
@@ -32290,7 +32320,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15">
       <c r="A134">
         <v>133</v>
       </c>
@@ -32337,7 +32367,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15">
       <c r="A135">
         <v>134</v>
       </c>
@@ -32384,7 +32414,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15">
       <c r="A136">
         <v>135</v>
       </c>
@@ -32431,7 +32461,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15">
       <c r="A137">
         <v>136</v>
       </c>
@@ -32478,7 +32508,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15">
       <c r="A138">
         <v>137</v>
       </c>
@@ -32525,7 +32555,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15">
       <c r="A139">
         <v>138</v>
       </c>
@@ -32572,7 +32602,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15">
       <c r="A140">
         <v>139</v>
       </c>
@@ -32619,7 +32649,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15">
       <c r="A141">
         <v>140</v>
       </c>
@@ -32666,7 +32696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15">
       <c r="A142">
         <v>141</v>
       </c>
@@ -32713,7 +32743,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15">
       <c r="A143">
         <v>142</v>
       </c>
@@ -32760,7 +32790,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15">
       <c r="A144">
         <v>143</v>
       </c>
@@ -32807,7 +32837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15">
       <c r="A145">
         <v>144</v>
       </c>
@@ -32854,7 +32884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15">
       <c r="A146">
         <v>145</v>
       </c>
@@ -32901,7 +32931,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15">
       <c r="A147">
         <v>146</v>
       </c>
@@ -32948,7 +32978,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15">
       <c r="A148">
         <v>147</v>
       </c>
@@ -32995,7 +33025,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15">
       <c r="A149">
         <v>148</v>
       </c>
@@ -33042,7 +33072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15">
       <c r="A150">
         <v>149</v>
       </c>
@@ -33089,7 +33119,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15">
       <c r="A151">
         <v>150</v>
       </c>
@@ -33136,7 +33166,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15">
       <c r="A152">
         <v>151</v>
       </c>
@@ -33183,7 +33213,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15">
       <c r="A153">
         <v>152</v>
       </c>
@@ -33230,7 +33260,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15">
       <c r="A154">
         <v>153</v>
       </c>
@@ -33277,7 +33307,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15">
       <c r="A155">
         <v>154</v>
       </c>
@@ -33324,7 +33354,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15">
       <c r="A156">
         <v>155</v>
       </c>
@@ -33371,7 +33401,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15">
       <c r="A157">
         <v>156</v>
       </c>
@@ -33418,7 +33448,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15">
       <c r="A158">
         <v>157</v>
       </c>
@@ -33465,7 +33495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15">
       <c r="A159">
         <v>158</v>
       </c>
@@ -33512,7 +33542,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15">
       <c r="A160">
         <v>159</v>
       </c>
@@ -33559,7 +33589,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:15">
       <c r="A161">
         <v>160</v>
       </c>
@@ -33606,7 +33636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:15">
       <c r="A162">
         <v>161</v>
       </c>
@@ -33653,7 +33683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:15">
       <c r="A163">
         <v>162</v>
       </c>
@@ -33700,7 +33730,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:15">
       <c r="A164">
         <v>163</v>
       </c>
@@ -33747,7 +33777,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:15">
       <c r="A165">
         <v>164</v>
       </c>
@@ -33794,7 +33824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:15">
       <c r="A166">
         <v>165</v>
       </c>
@@ -33841,7 +33871,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:15">
       <c r="A167">
         <v>166</v>
       </c>
@@ -33888,7 +33918,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:15">
       <c r="A168">
         <v>167</v>
       </c>
@@ -33935,7 +33965,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:15">
       <c r="A169">
         <v>168</v>
       </c>
@@ -33982,7 +34012,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:15">
       <c r="A170">
         <v>169</v>
       </c>
@@ -34029,7 +34059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:15">
       <c r="A171">
         <v>170</v>
       </c>
@@ -34076,7 +34106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:15">
       <c r="A172">
         <v>171</v>
       </c>
@@ -34123,7 +34153,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15">
       <c r="A173">
         <v>172</v>
       </c>
@@ -34170,7 +34200,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15">
       <c r="A174">
         <v>173</v>
       </c>
@@ -34217,7 +34247,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:15">
       <c r="A175">
         <v>174</v>
       </c>
@@ -34264,7 +34294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:15">
       <c r="A176">
         <v>175</v>
       </c>
@@ -34311,7 +34341,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15">
       <c r="A177">
         <v>176</v>
       </c>
@@ -34358,7 +34388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:15">
       <c r="A178">
         <v>177</v>
       </c>
@@ -34405,7 +34435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:15">
       <c r="A179">
         <v>178</v>
       </c>
@@ -34452,7 +34482,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:15">
       <c r="A180">
         <v>179</v>
       </c>
@@ -34499,7 +34529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:15">
       <c r="A181">
         <v>180</v>
       </c>
@@ -34546,7 +34576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:15">
       <c r="A182">
         <v>181</v>
       </c>
@@ -34593,7 +34623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:15">
       <c r="A183">
         <v>182</v>
       </c>
@@ -34640,7 +34670,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:15">
       <c r="A184">
         <v>183</v>
       </c>
@@ -34687,7 +34717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15">
       <c r="A185">
         <v>184</v>
       </c>
@@ -34734,7 +34764,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:15">
       <c r="A186">
         <v>185</v>
       </c>
@@ -34781,7 +34811,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:15">
       <c r="A187">
         <v>186</v>
       </c>
@@ -34828,7 +34858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:15">
       <c r="A188">
         <v>187</v>
       </c>
@@ -34875,7 +34905,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:15">
       <c r="A189">
         <v>188</v>
       </c>
@@ -34922,7 +34952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:15">
       <c r="A190">
         <v>189</v>
       </c>
@@ -34969,7 +34999,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:15">
       <c r="A191">
         <v>190</v>
       </c>
@@ -35016,7 +35046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15">
       <c r="A192">
         <v>191</v>
       </c>
@@ -35063,7 +35093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:15">
       <c r="A193">
         <v>192</v>
       </c>
@@ -35110,7 +35140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:15">
       <c r="A194">
         <v>193</v>
       </c>
@@ -35157,7 +35187,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:15">
       <c r="A195">
         <v>194</v>
       </c>
@@ -35204,7 +35234,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:15">
       <c r="A196">
         <v>195</v>
       </c>
@@ -35251,7 +35281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:15">
       <c r="A197">
         <v>196</v>
       </c>
@@ -35298,7 +35328,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:15">
       <c r="A198">
         <v>197</v>
       </c>
@@ -35345,7 +35375,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:15">
       <c r="A199">
         <v>198</v>
       </c>
@@ -35392,7 +35422,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:15">
       <c r="A200">
         <v>199</v>
       </c>
@@ -35439,7 +35469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:15">
       <c r="A201">
         <v>200</v>
       </c>
@@ -35486,7 +35516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15">
       <c r="A202">
         <v>201</v>
       </c>
@@ -35533,7 +35563,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15">
       <c r="A203">
         <v>202</v>
       </c>
@@ -35580,7 +35610,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:15">
       <c r="A204">
         <v>203</v>
       </c>
@@ -35627,7 +35657,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:15">
       <c r="A205">
         <v>204</v>
       </c>
@@ -35674,7 +35704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:15">
       <c r="A206">
         <v>205</v>
       </c>
@@ -35721,7 +35751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:15">
       <c r="A207">
         <v>206</v>
       </c>
@@ -35768,7 +35798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:15">
       <c r="A208">
         <v>207</v>
       </c>
@@ -35815,7 +35845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:15">
       <c r="A209">
         <v>208</v>
       </c>
@@ -35862,7 +35892,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:15">
       <c r="A210">
         <v>209</v>
       </c>
@@ -35909,7 +35939,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:15">
       <c r="A211">
         <v>210</v>
       </c>
@@ -35956,7 +35986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:15">
       <c r="A212">
         <v>211</v>
       </c>
@@ -36003,7 +36033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:15">
       <c r="A213">
         <v>212</v>
       </c>
@@ -36050,7 +36080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:15">
       <c r="A214">
         <v>213</v>
       </c>
@@ -36097,7 +36127,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:15">
       <c r="A215">
         <v>214</v>
       </c>
@@ -36144,7 +36174,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:15">
       <c r="A216">
         <v>215</v>
       </c>
@@ -36191,7 +36221,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:15">
       <c r="A217">
         <v>216</v>
       </c>
@@ -36238,7 +36268,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:15">
       <c r="A218">
         <v>217</v>
       </c>
@@ -36285,7 +36315,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:15">
       <c r="A219">
         <v>218</v>
       </c>
@@ -36332,7 +36362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:15">
       <c r="A220">
         <v>219</v>
       </c>
@@ -36379,7 +36409,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:15">
       <c r="A221">
         <v>220</v>
       </c>
@@ -36426,7 +36456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:15">
       <c r="A222">
         <v>221</v>
       </c>
@@ -36473,7 +36503,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:15">
       <c r="A223">
         <v>222</v>
       </c>
@@ -36520,7 +36550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:15">
       <c r="A224">
         <v>223</v>
       </c>
@@ -36567,7 +36597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:15">
       <c r="A225">
         <v>224</v>
       </c>
@@ -36614,7 +36644,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:15">
       <c r="A226">
         <v>225</v>
       </c>
@@ -36661,7 +36691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:15">
       <c r="A227">
         <v>226</v>
       </c>
@@ -36708,7 +36738,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:15">
       <c r="A228">
         <v>227</v>
       </c>
@@ -36755,7 +36785,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:15">
       <c r="A229">
         <v>228</v>
       </c>
@@ -36802,7 +36832,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:15">
       <c r="A230">
         <v>229</v>
       </c>
@@ -36849,7 +36879,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15">
       <c r="A231">
         <v>230</v>
       </c>
@@ -36896,7 +36926,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15">
       <c r="A232">
         <v>231</v>
       </c>
@@ -36943,7 +36973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:15">
       <c r="A233">
         <v>232</v>
       </c>
@@ -36990,7 +37020,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:15">
       <c r="A234">
         <v>233</v>
       </c>
@@ -37037,7 +37067,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:15">
       <c r="A235">
         <v>234</v>
       </c>
@@ -37084,7 +37114,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:15">
       <c r="A236">
         <v>235</v>
       </c>
@@ -37131,7 +37161,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:15">
       <c r="A237">
         <v>236</v>
       </c>
@@ -37178,7 +37208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:15">
       <c r="A238">
         <v>237</v>
       </c>
@@ -37225,7 +37255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:15">
       <c r="A239">
         <v>238</v>
       </c>
@@ -37272,7 +37302,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:15">
       <c r="A240">
         <v>239</v>
       </c>
@@ -37319,7 +37349,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:15">
       <c r="A241">
         <v>240</v>
       </c>
@@ -37366,7 +37396,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:15">
       <c r="A242">
         <v>241</v>
       </c>
@@ -37413,7 +37443,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:15">
       <c r="A243">
         <v>242</v>
       </c>
@@ -37460,7 +37490,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:15">
       <c r="A244">
         <v>243</v>
       </c>
@@ -37507,7 +37537,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:15">
       <c r="A245">
         <v>244</v>
       </c>
@@ -37554,7 +37584,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:15">
       <c r="A246">
         <v>245</v>
       </c>
@@ -37601,7 +37631,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:15">
       <c r="A247">
         <v>246</v>
       </c>
@@ -37648,7 +37678,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:15">
       <c r="A248">
         <v>247</v>
       </c>
@@ -37695,7 +37725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:15">
       <c r="A249">
         <v>248</v>
       </c>
@@ -37742,7 +37772,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:15">
       <c r="A250">
         <v>249</v>
       </c>
@@ -37789,7 +37819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:15">
       <c r="A251">
         <v>250</v>
       </c>
@@ -37836,7 +37866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:15">
       <c r="A252">
         <v>251</v>
       </c>
@@ -37883,7 +37913,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:15">
       <c r="A253">
         <v>252</v>
       </c>
@@ -37930,7 +37960,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:15">
       <c r="A254">
         <v>253</v>
       </c>
@@ -37977,7 +38007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:15">
       <c r="A255">
         <v>254</v>
       </c>
@@ -38024,7 +38054,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:15">
       <c r="A256">
         <v>255</v>
       </c>
@@ -38071,7 +38101,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:15">
       <c r="A257">
         <v>256</v>
       </c>
@@ -38118,7 +38148,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:15">
       <c r="A258">
         <v>257</v>
       </c>
@@ -38165,7 +38195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:15">
       <c r="A259">
         <v>258</v>
       </c>
@@ -38212,7 +38242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15">
       <c r="A260">
         <v>259</v>
       </c>
@@ -38259,7 +38289,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15">
       <c r="A261">
         <v>260</v>
       </c>
@@ -38306,7 +38336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:15">
       <c r="A262">
         <v>261</v>
       </c>
@@ -38353,7 +38383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:15">
       <c r="A263">
         <v>262</v>
       </c>
@@ -38400,7 +38430,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:15">
       <c r="A264">
         <v>263</v>
       </c>
@@ -38447,7 +38477,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:15">
       <c r="A265">
         <v>264</v>
       </c>
@@ -38494,7 +38524,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:15">
       <c r="A266">
         <v>265</v>
       </c>
@@ -38541,7 +38571,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:15">
       <c r="A267">
         <v>266</v>
       </c>
@@ -38588,7 +38618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:15">
       <c r="A268">
         <v>267</v>
       </c>
@@ -38635,7 +38665,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:15">
       <c r="A269">
         <v>268</v>
       </c>
@@ -38682,7 +38712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:15">
       <c r="A270">
         <v>269</v>
       </c>
@@ -38729,7 +38759,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:15">
       <c r="A271">
         <v>270</v>
       </c>
@@ -38776,7 +38806,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:15">
       <c r="A272">
         <v>271</v>
       </c>
@@ -38823,7 +38853,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:15">
       <c r="A273">
         <v>272</v>
       </c>
@@ -38870,7 +38900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:15">
       <c r="A274">
         <v>273</v>
       </c>
@@ -38917,7 +38947,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:15">
       <c r="A275">
         <v>274</v>
       </c>
@@ -38964,7 +38994,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:15">
       <c r="A276">
         <v>275</v>
       </c>
@@ -39011,7 +39041,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:15">
       <c r="A277">
         <v>276</v>
       </c>
@@ -39058,7 +39088,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:15">
       <c r="A278">
         <v>277</v>
       </c>
@@ -39105,7 +39135,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:15">
       <c r="A279">
         <v>278</v>
       </c>
@@ -39152,7 +39182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:15">
       <c r="A280">
         <v>279</v>
       </c>
@@ -39199,7 +39229,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:15">
       <c r="A281">
         <v>280</v>
       </c>
@@ -39246,7 +39276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:15">
       <c r="A282">
         <v>281</v>
       </c>
@@ -39293,7 +39323,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:15">
       <c r="A283">
         <v>282</v>
       </c>
@@ -39340,7 +39370,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="284" spans="1:15" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:15" s="8" customFormat="1">
       <c r="A284" s="8">
         <v>283</v>
       </c>
@@ -39388,22 +39418,22 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O1"/>
+  <autoFilter ref="A1:O1" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="26" style="9" customWidth="1"/>
     <col min="2" max="2" width="82" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="11" customFormat="1">
       <c r="A1" s="9" t="s">
         <v>2472</v>
       </c>
@@ -39411,7 +39441,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" s="9" t="s">
         <v>2474</v>
       </c>
@@ -39419,7 +39449,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
         <v>13</v>
       </c>
@@ -39427,7 +39457,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="29">
       <c r="A4" s="9" t="s">
         <v>2476</v>
       </c>
@@ -39435,7 +39465,7 @@
         <v>2477</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
         <v>2473</v>
       </c>
@@ -39443,7 +39473,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="6" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" s="11" customFormat="1">
       <c r="A6" s="9" t="s">
         <v>2478</v>
       </c>
@@ -39451,7 +39481,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="29">
       <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
@@ -39459,7 +39489,7 @@
         <v>2479</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
@@ -39467,7 +39497,7 @@
         <v>2480</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="29">
       <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
@@ -39475,7 +39505,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
         <v>2473</v>
       </c>
@@ -39483,7 +39513,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="11" spans="1:2" s="11" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" s="11" customFormat="1">
       <c r="A11" s="9" t="s">
         <v>2482</v>
       </c>
@@ -39491,7 +39521,7 @@
         <v>2473</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
         <v>2483</v>
       </c>
@@ -39499,7 +39529,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="29">
       <c r="A13" s="9" t="s">
         <v>2485</v>
       </c>
@@ -39509,6 +39539,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>